--- a/business_forms/038_cost_allocation_change_request_form--business_forms.xlsx
+++ b/business_forms/038_cost_allocation_change_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'type_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'type_1'}</t>
+          <t>type 1</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'type_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'type_2'}</t>
+          <t>type 2</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'type_3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'type_3'}</t>
+          <t>type 3</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'type_4'}</t>
+          <t>type_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'type_4'}</t>
+          <t>type 4</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'type_5'}</t>
+          <t>type_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'type_5'}</t>
+          <t>type 5</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'status_1'}</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'status_1'}</t>
+          <t>status 1</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'status_2'}</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'status_2'}</t>
+          <t>status 2</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'status_3'}</t>
+          <t>status_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'status_3'}</t>
+          <t>status 3</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'status_4'}</t>
+          <t>status_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'status_4'}</t>
+          <t>status 4</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'status_5'}</t>
+          <t>status_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'status_5'}</t>
+          <t>status 5</t>
         </is>
       </c>
     </row>
